--- a/app/模板/结算模板/【大连游者之家】结算单_发行部韩语本地化需求26年2&3月模板.xlsx
+++ b/app/模板/结算模板/【大连游者之家】结算单_发行部韩语本地化需求26年2&3月模板.xlsx
@@ -82,7 +82,7 @@
   <si>
     <t>公司： 广州库洛科技有限公司
 纳税人识别号：91440101MA59JPNR3D
-开票项目： 现代服务*翻译服务费
+开票项目： 生产生活服务*翻译服务
 电话： 020-85655091
 银行账号： 120912143410201
 开户银行： 招行广州科技园支行</t>
@@ -1029,7 +1029,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1150,9 +1150,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="178" fontId="9" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1993,8 +1990,8 @@
     </row>
     <row r="20" s="2" customFormat="1" spans="2:12">
       <c r="B20" s="40"/>
-      <c r="C20" s="41"/>
-      <c r="D20" s="41"/>
+      <c r="C20" s="33"/>
+      <c r="D20" s="33"/>
       <c r="E20" s="34"/>
       <c r="F20" s="35"/>
       <c r="G20" s="35"/>
@@ -2014,8 +2011,8 @@
     </row>
     <row r="21" s="2" customFormat="1" spans="2:12">
       <c r="B21" s="40"/>
-      <c r="C21" s="41"/>
-      <c r="D21" s="41"/>
+      <c r="C21" s="33"/>
+      <c r="D21" s="33"/>
       <c r="E21" s="34"/>
       <c r="F21" s="35"/>
       <c r="G21" s="35"/>
@@ -2035,8 +2032,8 @@
     </row>
     <row r="22" s="2" customFormat="1" spans="2:12">
       <c r="B22" s="40"/>
-      <c r="C22" s="41"/>
-      <c r="D22" s="41"/>
+      <c r="C22" s="33"/>
+      <c r="D22" s="33"/>
       <c r="E22" s="34"/>
       <c r="F22" s="35"/>
       <c r="G22" s="35"/>
@@ -2056,8 +2053,8 @@
     </row>
     <row r="23" s="2" customFormat="1" spans="2:12">
       <c r="B23" s="40"/>
-      <c r="C23" s="41"/>
-      <c r="D23" s="41"/>
+      <c r="C23" s="33"/>
+      <c r="D23" s="33"/>
       <c r="E23" s="34"/>
       <c r="F23" s="35"/>
       <c r="G23" s="35"/>
@@ -2077,8 +2074,8 @@
     </row>
     <row r="24" s="2" customFormat="1" spans="2:12">
       <c r="B24" s="40"/>
-      <c r="C24" s="41"/>
-      <c r="D24" s="41"/>
+      <c r="C24" s="33"/>
+      <c r="D24" s="33"/>
       <c r="E24" s="34"/>
       <c r="F24" s="35"/>
       <c r="G24" s="35"/>
@@ -2098,8 +2095,8 @@
     </row>
     <row r="25" s="2" customFormat="1" spans="2:12">
       <c r="B25" s="40"/>
-      <c r="C25" s="41"/>
-      <c r="D25" s="41"/>
+      <c r="C25" s="33"/>
+      <c r="D25" s="33"/>
       <c r="E25" s="34"/>
       <c r="F25" s="35"/>
       <c r="G25" s="35"/>
@@ -2119,8 +2116,8 @@
     </row>
     <row r="26" s="2" customFormat="1" spans="2:12">
       <c r="B26" s="40"/>
-      <c r="C26" s="41"/>
-      <c r="D26" s="41"/>
+      <c r="C26" s="33"/>
+      <c r="D26" s="33"/>
       <c r="E26" s="34"/>
       <c r="F26" s="35"/>
       <c r="G26" s="35"/>
@@ -2140,8 +2137,8 @@
     </row>
     <row r="27" s="2" customFormat="1" spans="2:12">
       <c r="B27" s="40"/>
-      <c r="C27" s="41"/>
-      <c r="D27" s="41"/>
+      <c r="C27" s="33"/>
+      <c r="D27" s="33"/>
       <c r="E27" s="34"/>
       <c r="F27" s="35"/>
       <c r="G27" s="35"/>
@@ -2161,8 +2158,8 @@
     </row>
     <row r="28" s="2" customFormat="1" spans="2:12">
       <c r="B28" s="40"/>
-      <c r="C28" s="41"/>
-      <c r="D28" s="41"/>
+      <c r="C28" s="33"/>
+      <c r="D28" s="33"/>
       <c r="E28" s="34"/>
       <c r="F28" s="35"/>
       <c r="G28" s="35"/>
@@ -2182,8 +2179,8 @@
     </row>
     <row r="29" s="2" customFormat="1" spans="2:12">
       <c r="B29" s="40"/>
-      <c r="C29" s="41"/>
-      <c r="D29" s="41"/>
+      <c r="C29" s="33"/>
+      <c r="D29" s="33"/>
       <c r="E29" s="34"/>
       <c r="F29" s="35"/>
       <c r="G29" s="35"/>
@@ -2203,8 +2200,8 @@
     </row>
     <row r="30" s="2" customFormat="1" spans="2:12">
       <c r="B30" s="40"/>
-      <c r="C30" s="41"/>
-      <c r="D30" s="41"/>
+      <c r="C30" s="33"/>
+      <c r="D30" s="33"/>
       <c r="E30" s="34"/>
       <c r="F30" s="35"/>
       <c r="G30" s="35"/>
@@ -2224,8 +2221,8 @@
     </row>
     <row r="31" s="2" customFormat="1" spans="2:12">
       <c r="B31" s="40"/>
-      <c r="C31" s="41"/>
-      <c r="D31" s="41"/>
+      <c r="C31" s="33"/>
+      <c r="D31" s="33"/>
       <c r="E31" s="34"/>
       <c r="F31" s="35"/>
       <c r="G31" s="35"/>
@@ -2245,8 +2242,8 @@
     </row>
     <row r="32" s="2" customFormat="1" spans="2:12">
       <c r="B32" s="40"/>
-      <c r="C32" s="41"/>
-      <c r="D32" s="41"/>
+      <c r="C32" s="33"/>
+      <c r="D32" s="33"/>
       <c r="E32" s="34"/>
       <c r="F32" s="35"/>
       <c r="G32" s="35"/>
@@ -2266,8 +2263,8 @@
     </row>
     <row r="33" s="2" customFormat="1" spans="2:12">
       <c r="B33" s="40"/>
-      <c r="C33" s="41"/>
-      <c r="D33" s="41"/>
+      <c r="C33" s="33"/>
+      <c r="D33" s="33"/>
       <c r="E33" s="34"/>
       <c r="F33" s="35"/>
       <c r="G33" s="35"/>
@@ -2287,8 +2284,8 @@
     </row>
     <row r="34" s="2" customFormat="1" spans="2:12">
       <c r="B34" s="40"/>
-      <c r="C34" s="41"/>
-      <c r="D34" s="41"/>
+      <c r="C34" s="33"/>
+      <c r="D34" s="33"/>
       <c r="E34" s="34"/>
       <c r="F34" s="35"/>
       <c r="G34" s="35"/>
@@ -2308,8 +2305,8 @@
     </row>
     <row r="35" s="2" customFormat="1" spans="2:12">
       <c r="B35" s="40"/>
-      <c r="C35" s="41"/>
-      <c r="D35" s="41"/>
+      <c r="C35" s="33"/>
+      <c r="D35" s="33"/>
       <c r="E35" s="34"/>
       <c r="F35" s="35"/>
       <c r="G35" s="35"/>
@@ -2329,8 +2326,8 @@
     </row>
     <row r="36" s="2" customFormat="1" spans="2:12">
       <c r="B36" s="40"/>
-      <c r="C36" s="41"/>
-      <c r="D36" s="41"/>
+      <c r="C36" s="33"/>
+      <c r="D36" s="33"/>
       <c r="E36" s="34"/>
       <c r="F36" s="35"/>
       <c r="G36" s="35"/>
@@ -2350,8 +2347,8 @@
     </row>
     <row r="37" s="2" customFormat="1" spans="2:12">
       <c r="B37" s="40"/>
-      <c r="C37" s="41"/>
-      <c r="D37" s="41"/>
+      <c r="C37" s="33"/>
+      <c r="D37" s="33"/>
       <c r="E37" s="34"/>
       <c r="F37" s="35"/>
       <c r="G37" s="35"/>
@@ -2371,8 +2368,8 @@
     </row>
     <row r="38" s="2" customFormat="1" spans="2:12">
       <c r="B38" s="40"/>
-      <c r="C38" s="41"/>
-      <c r="D38" s="41"/>
+      <c r="C38" s="33"/>
+      <c r="D38" s="33"/>
       <c r="E38" s="34"/>
       <c r="F38" s="35"/>
       <c r="G38" s="35"/>
@@ -2392,8 +2389,8 @@
     </row>
     <row r="39" s="2" customFormat="1" spans="2:12">
       <c r="B39" s="40"/>
-      <c r="C39" s="41"/>
-      <c r="D39" s="41"/>
+      <c r="C39" s="33"/>
+      <c r="D39" s="33"/>
       <c r="E39" s="34"/>
       <c r="F39" s="35"/>
       <c r="G39" s="35"/>
@@ -2413,8 +2410,8 @@
     </row>
     <row r="40" s="2" customFormat="1" spans="2:12">
       <c r="B40" s="40"/>
-      <c r="C40" s="41"/>
-      <c r="D40" s="41"/>
+      <c r="C40" s="33"/>
+      <c r="D40" s="33"/>
       <c r="E40" s="34"/>
       <c r="F40" s="35"/>
       <c r="G40" s="35"/>
@@ -2434,8 +2431,8 @@
     </row>
     <row r="41" s="2" customFormat="1" spans="2:12">
       <c r="B41" s="40"/>
-      <c r="C41" s="41"/>
-      <c r="D41" s="41"/>
+      <c r="C41" s="33"/>
+      <c r="D41" s="33"/>
       <c r="E41" s="34"/>
       <c r="F41" s="35"/>
       <c r="G41" s="35"/>
@@ -2833,13 +2830,13 @@
     </row>
     <row r="60" s="2" customFormat="1" spans="2:18">
       <c r="B60" s="40"/>
-      <c r="C60" s="42" t="s">
+      <c r="C60" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="D60" s="42"/>
-      <c r="E60" s="42"/>
-      <c r="F60" s="43"/>
-      <c r="G60" s="43"/>
+      <c r="D60" s="41"/>
+      <c r="E60" s="41"/>
+      <c r="F60" s="42"/>
+      <c r="G60" s="42"/>
       <c r="H60" s="36">
         <f>SUM(H10:H59)</f>
         <v>0</v>
@@ -2849,7 +2846,7 @@
         <f>SUM(J10:J59)</f>
         <v>0</v>
       </c>
-      <c r="K60" s="44">
+      <c r="K60" s="43">
         <v>0.06</v>
       </c>
       <c r="L60" s="39">
@@ -2859,313 +2856,313 @@
     </row>
     <row r="61" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:18">
       <c r="B61" s="40"/>
-      <c r="C61" s="45"/>
-      <c r="D61" s="45"/>
-      <c r="E61" s="45"/>
-      <c r="F61" s="45"/>
-      <c r="G61" s="45"/>
-      <c r="H61" s="45"/>
-      <c r="I61" s="45"/>
-      <c r="J61" s="45"/>
-      <c r="K61" s="45"/>
-      <c r="L61" s="46"/>
+      <c r="C61" s="44"/>
+      <c r="D61" s="44"/>
+      <c r="E61" s="44"/>
+      <c r="F61" s="44"/>
+      <c r="G61" s="44"/>
+      <c r="H61" s="44"/>
+      <c r="I61" s="44"/>
+      <c r="J61" s="44"/>
+      <c r="K61" s="44"/>
+      <c r="L61" s="45"/>
     </row>
     <row r="62" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:18">
       <c r="B62" s="40"/>
-      <c r="C62" s="47" t="s">
+      <c r="C62" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="D62" s="48" t="s">
+      <c r="D62" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="E62" s="48"/>
-      <c r="F62" s="48"/>
-      <c r="G62" s="48"/>
-      <c r="H62" s="48"/>
-      <c r="I62" s="48"/>
-      <c r="J62" s="48"/>
-      <c r="K62" s="48"/>
-      <c r="L62" s="49"/>
-      <c r="M62" s="50"/>
-      <c r="N62" s="50"/>
-      <c r="O62" s="50"/>
-      <c r="P62" s="50"/>
-      <c r="Q62" s="50"/>
-      <c r="R62" s="50"/>
+      <c r="E62" s="47"/>
+      <c r="F62" s="47"/>
+      <c r="G62" s="47"/>
+      <c r="H62" s="47"/>
+      <c r="I62" s="47"/>
+      <c r="J62" s="47"/>
+      <c r="K62" s="47"/>
+      <c r="L62" s="48"/>
+      <c r="M62" s="49"/>
+      <c r="N62" s="49"/>
+      <c r="O62" s="49"/>
+      <c r="P62" s="49"/>
+      <c r="Q62" s="49"/>
+      <c r="R62" s="49"/>
     </row>
     <row r="63" ht="18.75" customHeight="1" spans="2:18">
       <c r="B63" s="28"/>
-      <c r="C63" s="51" t="s">
+      <c r="C63" s="50" t="s">
         <v>15</v>
       </c>
-      <c r="D63" s="51"/>
-      <c r="E63" s="51"/>
-      <c r="F63" s="51"/>
-      <c r="G63" s="51"/>
-      <c r="H63" s="51"/>
-      <c r="I63" s="51"/>
-      <c r="J63" s="51"/>
-      <c r="K63" s="51"/>
-      <c r="L63" s="52"/>
-      <c r="M63" s="53"/>
-      <c r="N63" s="53"/>
-      <c r="O63" s="53"/>
-      <c r="P63" s="53"/>
-      <c r="Q63" s="53"/>
-      <c r="R63" s="53"/>
+      <c r="D63" s="50"/>
+      <c r="E63" s="50"/>
+      <c r="F63" s="50"/>
+      <c r="G63" s="50"/>
+      <c r="H63" s="50"/>
+      <c r="I63" s="50"/>
+      <c r="J63" s="50"/>
+      <c r="K63" s="50"/>
+      <c r="L63" s="51"/>
+      <c r="M63" s="52"/>
+      <c r="N63" s="52"/>
+      <c r="O63" s="52"/>
+      <c r="P63" s="52"/>
+      <c r="Q63" s="52"/>
+      <c r="R63" s="52"/>
     </row>
     <row r="64" spans="2:18">
       <c r="B64" s="28"/>
-      <c r="C64" s="54" t="s">
+      <c r="C64" s="53" t="s">
         <v>16</v>
       </c>
-      <c r="D64" s="54"/>
-      <c r="E64" s="54"/>
-      <c r="F64" s="54"/>
-      <c r="G64" s="54"/>
-      <c r="H64" s="54"/>
-      <c r="I64" s="54"/>
-      <c r="J64" s="54"/>
-      <c r="K64" s="54"/>
-      <c r="L64" s="55"/>
-      <c r="M64" s="53"/>
-      <c r="N64" s="53"/>
-      <c r="O64" s="53"/>
-      <c r="P64" s="53"/>
-      <c r="Q64" s="53"/>
-      <c r="R64" s="53"/>
+      <c r="D64" s="53"/>
+      <c r="E64" s="53"/>
+      <c r="F64" s="53"/>
+      <c r="G64" s="53"/>
+      <c r="H64" s="53"/>
+      <c r="I64" s="53"/>
+      <c r="J64" s="53"/>
+      <c r="K64" s="53"/>
+      <c r="L64" s="54"/>
+      <c r="M64" s="52"/>
+      <c r="N64" s="52"/>
+      <c r="O64" s="52"/>
+      <c r="P64" s="52"/>
+      <c r="Q64" s="52"/>
+      <c r="R64" s="52"/>
     </row>
     <row r="65" ht="20.25" customHeight="1" spans="2:18">
       <c r="B65" s="28"/>
-      <c r="C65" s="54"/>
-      <c r="D65" s="54"/>
-      <c r="E65" s="54"/>
-      <c r="F65" s="54"/>
-      <c r="G65" s="54"/>
-      <c r="H65" s="54"/>
-      <c r="I65" s="54"/>
-      <c r="J65" s="54"/>
-      <c r="K65" s="54"/>
-      <c r="L65" s="55"/>
-      <c r="M65" s="53"/>
-      <c r="N65" s="53"/>
-      <c r="O65" s="53"/>
-      <c r="P65" s="53"/>
-      <c r="Q65" s="53"/>
-      <c r="R65" s="53"/>
+      <c r="C65" s="53"/>
+      <c r="D65" s="53"/>
+      <c r="E65" s="53"/>
+      <c r="F65" s="53"/>
+      <c r="G65" s="53"/>
+      <c r="H65" s="53"/>
+      <c r="I65" s="53"/>
+      <c r="J65" s="53"/>
+      <c r="K65" s="53"/>
+      <c r="L65" s="54"/>
+      <c r="M65" s="52"/>
+      <c r="N65" s="52"/>
+      <c r="O65" s="52"/>
+      <c r="P65" s="52"/>
+      <c r="Q65" s="52"/>
+      <c r="R65" s="52"/>
     </row>
     <row r="66" ht="20.25" customHeight="1" spans="2:18">
       <c r="B66" s="28"/>
-      <c r="C66" s="54"/>
-      <c r="D66" s="54"/>
-      <c r="E66" s="54"/>
-      <c r="F66" s="54"/>
-      <c r="G66" s="54"/>
-      <c r="H66" s="54"/>
-      <c r="I66" s="54"/>
-      <c r="J66" s="54"/>
-      <c r="K66" s="54"/>
-      <c r="L66" s="55"/>
-      <c r="M66" s="53"/>
-      <c r="N66" s="53"/>
-      <c r="O66" s="53"/>
-      <c r="P66" s="53"/>
-      <c r="Q66" s="53"/>
-      <c r="R66" s="53"/>
+      <c r="C66" s="53"/>
+      <c r="D66" s="53"/>
+      <c r="E66" s="53"/>
+      <c r="F66" s="53"/>
+      <c r="G66" s="53"/>
+      <c r="H66" s="53"/>
+      <c r="I66" s="53"/>
+      <c r="J66" s="53"/>
+      <c r="K66" s="53"/>
+      <c r="L66" s="54"/>
+      <c r="M66" s="52"/>
+      <c r="N66" s="52"/>
+      <c r="O66" s="52"/>
+      <c r="P66" s="52"/>
+      <c r="Q66" s="52"/>
+      <c r="R66" s="52"/>
     </row>
     <row r="67" ht="20.25" customHeight="1" spans="2:18">
       <c r="B67" s="28"/>
-      <c r="C67" s="54"/>
-      <c r="D67" s="54"/>
-      <c r="E67" s="54"/>
-      <c r="F67" s="54"/>
-      <c r="G67" s="54"/>
-      <c r="H67" s="54"/>
-      <c r="I67" s="54"/>
-      <c r="J67" s="54"/>
-      <c r="K67" s="54"/>
-      <c r="L67" s="55"/>
-      <c r="M67" s="53"/>
-      <c r="N67" s="53"/>
-      <c r="O67" s="53"/>
-      <c r="P67" s="53"/>
-      <c r="Q67" s="53"/>
-      <c r="R67" s="53"/>
+      <c r="C67" s="53"/>
+      <c r="D67" s="53"/>
+      <c r="E67" s="53"/>
+      <c r="F67" s="53"/>
+      <c r="G67" s="53"/>
+      <c r="H67" s="53"/>
+      <c r="I67" s="53"/>
+      <c r="J67" s="53"/>
+      <c r="K67" s="53"/>
+      <c r="L67" s="54"/>
+      <c r="M67" s="52"/>
+      <c r="N67" s="52"/>
+      <c r="O67" s="52"/>
+      <c r="P67" s="52"/>
+      <c r="Q67" s="52"/>
+      <c r="R67" s="52"/>
     </row>
     <row r="68" ht="20.25" customHeight="1" spans="2:18">
       <c r="B68" s="28"/>
-      <c r="C68" s="54"/>
-      <c r="D68" s="54"/>
-      <c r="E68" s="54"/>
-      <c r="F68" s="54"/>
-      <c r="G68" s="54"/>
-      <c r="H68" s="54"/>
-      <c r="I68" s="54"/>
-      <c r="J68" s="54"/>
-      <c r="K68" s="54"/>
-      <c r="L68" s="55"/>
-      <c r="M68" s="53"/>
-      <c r="N68" s="53"/>
-      <c r="O68" s="53"/>
-      <c r="P68" s="53"/>
-      <c r="Q68" s="53"/>
-      <c r="R68" s="53"/>
+      <c r="C68" s="53"/>
+      <c r="D68" s="53"/>
+      <c r="E68" s="53"/>
+      <c r="F68" s="53"/>
+      <c r="G68" s="53"/>
+      <c r="H68" s="53"/>
+      <c r="I68" s="53"/>
+      <c r="J68" s="53"/>
+      <c r="K68" s="53"/>
+      <c r="L68" s="54"/>
+      <c r="M68" s="52"/>
+      <c r="N68" s="52"/>
+      <c r="O68" s="52"/>
+      <c r="P68" s="52"/>
+      <c r="Q68" s="52"/>
+      <c r="R68" s="52"/>
     </row>
     <row r="69" ht="20.25" customHeight="1" spans="2:18">
       <c r="B69" s="28"/>
-      <c r="C69" s="54"/>
-      <c r="D69" s="54"/>
-      <c r="E69" s="54"/>
-      <c r="F69" s="54"/>
-      <c r="G69" s="54"/>
-      <c r="H69" s="54"/>
-      <c r="I69" s="54"/>
-      <c r="J69" s="54"/>
-      <c r="K69" s="54"/>
-      <c r="L69" s="55"/>
-      <c r="M69" s="53"/>
-      <c r="N69" s="53"/>
-      <c r="O69" s="53"/>
-      <c r="P69" s="53"/>
-      <c r="Q69" s="53"/>
-      <c r="R69" s="53"/>
+      <c r="C69" s="53"/>
+      <c r="D69" s="53"/>
+      <c r="E69" s="53"/>
+      <c r="F69" s="53"/>
+      <c r="G69" s="53"/>
+      <c r="H69" s="53"/>
+      <c r="I69" s="53"/>
+      <c r="J69" s="53"/>
+      <c r="K69" s="53"/>
+      <c r="L69" s="54"/>
+      <c r="M69" s="52"/>
+      <c r="N69" s="52"/>
+      <c r="O69" s="52"/>
+      <c r="P69" s="52"/>
+      <c r="Q69" s="52"/>
+      <c r="R69" s="52"/>
     </row>
     <row r="70" ht="20.25" customHeight="1" spans="2:18">
       <c r="B70" s="28"/>
-      <c r="C70" s="56" t="s">
+      <c r="C70" s="55" t="s">
         <v>17</v>
       </c>
-      <c r="D70" s="57"/>
-      <c r="E70" s="57"/>
-      <c r="F70" s="58"/>
-      <c r="G70" s="58"/>
-      <c r="H70" s="57"/>
-      <c r="I70" s="57"/>
-      <c r="J70" s="57"/>
-      <c r="K70" s="57"/>
-      <c r="L70" s="59"/>
-      <c r="M70" s="53"/>
-      <c r="N70" s="53"/>
-      <c r="O70" s="53"/>
-      <c r="P70" s="53"/>
-      <c r="Q70" s="53"/>
-      <c r="R70" s="53"/>
+      <c r="D70" s="56"/>
+      <c r="E70" s="56"/>
+      <c r="F70" s="57"/>
+      <c r="G70" s="57"/>
+      <c r="H70" s="56"/>
+      <c r="I70" s="56"/>
+      <c r="J70" s="56"/>
+      <c r="K70" s="56"/>
+      <c r="L70" s="58"/>
+      <c r="M70" s="52"/>
+      <c r="N70" s="52"/>
+      <c r="O70" s="52"/>
+      <c r="P70" s="52"/>
+      <c r="Q70" s="52"/>
+      <c r="R70" s="52"/>
     </row>
     <row r="71" ht="20.25" customHeight="1" spans="2:18">
       <c r="B71" s="28"/>
-      <c r="C71" s="60" t="s">
+      <c r="C71" s="59" t="s">
         <v>18</v>
       </c>
-      <c r="D71" s="61"/>
-      <c r="E71" s="61"/>
-      <c r="F71" s="61"/>
-      <c r="G71" s="61"/>
-      <c r="H71" s="61"/>
-      <c r="I71" s="61"/>
-      <c r="J71" s="61"/>
-      <c r="K71" s="61"/>
-      <c r="L71" s="62"/>
-      <c r="M71" s="53"/>
-      <c r="N71" s="53"/>
-      <c r="O71" s="53"/>
-      <c r="P71" s="53"/>
-      <c r="Q71" s="53"/>
-      <c r="R71" s="53"/>
+      <c r="D71" s="60"/>
+      <c r="E71" s="60"/>
+      <c r="F71" s="60"/>
+      <c r="G71" s="60"/>
+      <c r="H71" s="60"/>
+      <c r="I71" s="60"/>
+      <c r="J71" s="60"/>
+      <c r="K71" s="60"/>
+      <c r="L71" s="61"/>
+      <c r="M71" s="52"/>
+      <c r="N71" s="52"/>
+      <c r="O71" s="52"/>
+      <c r="P71" s="52"/>
+      <c r="Q71" s="52"/>
+      <c r="R71" s="52"/>
     </row>
     <row r="72" ht="20.25" customHeight="1" spans="2:18">
       <c r="B72" s="28"/>
-      <c r="C72" s="61"/>
-      <c r="D72" s="61"/>
-      <c r="E72" s="61"/>
-      <c r="F72" s="61"/>
-      <c r="G72" s="61"/>
-      <c r="H72" s="61"/>
-      <c r="I72" s="61"/>
-      <c r="J72" s="61"/>
-      <c r="K72" s="61"/>
-      <c r="L72" s="62"/>
-      <c r="M72" s="53"/>
-      <c r="N72" s="53"/>
-      <c r="O72" s="53"/>
-      <c r="P72" s="53"/>
-      <c r="Q72" s="53"/>
-      <c r="R72" s="53"/>
+      <c r="C72" s="60"/>
+      <c r="D72" s="60"/>
+      <c r="E72" s="60"/>
+      <c r="F72" s="60"/>
+      <c r="G72" s="60"/>
+      <c r="H72" s="60"/>
+      <c r="I72" s="60"/>
+      <c r="J72" s="60"/>
+      <c r="K72" s="60"/>
+      <c r="L72" s="61"/>
+      <c r="M72" s="52"/>
+      <c r="N72" s="52"/>
+      <c r="O72" s="52"/>
+      <c r="P72" s="52"/>
+      <c r="Q72" s="52"/>
+      <c r="R72" s="52"/>
     </row>
     <row r="73" ht="20.25" customHeight="1" spans="2:18">
       <c r="B73" s="28"/>
-      <c r="C73" s="61"/>
-      <c r="D73" s="61"/>
-      <c r="E73" s="61"/>
-      <c r="F73" s="61"/>
-      <c r="G73" s="61"/>
-      <c r="H73" s="61"/>
-      <c r="I73" s="61"/>
-      <c r="J73" s="61"/>
-      <c r="K73" s="61"/>
-      <c r="L73" s="62"/>
-      <c r="M73" s="53"/>
-      <c r="N73" s="53"/>
-      <c r="O73" s="53"/>
-      <c r="P73" s="53"/>
-      <c r="Q73" s="53"/>
-      <c r="R73" s="53"/>
+      <c r="C73" s="60"/>
+      <c r="D73" s="60"/>
+      <c r="E73" s="60"/>
+      <c r="F73" s="60"/>
+      <c r="G73" s="60"/>
+      <c r="H73" s="60"/>
+      <c r="I73" s="60"/>
+      <c r="J73" s="60"/>
+      <c r="K73" s="60"/>
+      <c r="L73" s="61"/>
+      <c r="M73" s="52"/>
+      <c r="N73" s="52"/>
+      <c r="O73" s="52"/>
+      <c r="P73" s="52"/>
+      <c r="Q73" s="52"/>
+      <c r="R73" s="52"/>
     </row>
     <row r="74" ht="20.25" customHeight="1" spans="2:18">
       <c r="B74" s="28"/>
-      <c r="C74" s="61"/>
-      <c r="D74" s="61"/>
-      <c r="E74" s="61"/>
-      <c r="F74" s="61"/>
-      <c r="G74" s="61"/>
-      <c r="H74" s="61"/>
-      <c r="I74" s="61"/>
-      <c r="J74" s="61"/>
-      <c r="K74" s="61"/>
-      <c r="L74" s="62"/>
-      <c r="M74" s="53"/>
-      <c r="N74" s="53"/>
-      <c r="O74" s="53"/>
-      <c r="P74" s="53"/>
-      <c r="Q74" s="53"/>
-      <c r="R74" s="53"/>
+      <c r="C74" s="60"/>
+      <c r="D74" s="60"/>
+      <c r="E74" s="60"/>
+      <c r="F74" s="60"/>
+      <c r="G74" s="60"/>
+      <c r="H74" s="60"/>
+      <c r="I74" s="60"/>
+      <c r="J74" s="60"/>
+      <c r="K74" s="60"/>
+      <c r="L74" s="61"/>
+      <c r="M74" s="52"/>
+      <c r="N74" s="52"/>
+      <c r="O74" s="52"/>
+      <c r="P74" s="52"/>
+      <c r="Q74" s="52"/>
+      <c r="R74" s="52"/>
     </row>
     <row r="75" ht="15.75" customHeight="1" spans="2:18">
       <c r="B75" s="28"/>
-      <c r="C75" s="61"/>
-      <c r="D75" s="61"/>
-      <c r="E75" s="61"/>
-      <c r="F75" s="61"/>
-      <c r="G75" s="61"/>
-      <c r="H75" s="61"/>
-      <c r="I75" s="61"/>
-      <c r="J75" s="61"/>
-      <c r="K75" s="61"/>
-      <c r="L75" s="62"/>
-      <c r="M75" s="53"/>
-      <c r="N75" s="53"/>
-      <c r="O75" s="53"/>
-      <c r="P75" s="53"/>
-      <c r="Q75" s="53"/>
-      <c r="R75" s="53"/>
+      <c r="C75" s="60"/>
+      <c r="D75" s="60"/>
+      <c r="E75" s="60"/>
+      <c r="F75" s="60"/>
+      <c r="G75" s="60"/>
+      <c r="H75" s="60"/>
+      <c r="I75" s="60"/>
+      <c r="J75" s="60"/>
+      <c r="K75" s="60"/>
+      <c r="L75" s="61"/>
+      <c r="M75" s="52"/>
+      <c r="N75" s="52"/>
+      <c r="O75" s="52"/>
+      <c r="P75" s="52"/>
+      <c r="Q75" s="52"/>
+      <c r="R75" s="52"/>
     </row>
     <row r="76" ht="26.25" customHeight="1" spans="2:18">
       <c r="B76" s="28"/>
-      <c r="C76" s="61"/>
-      <c r="D76" s="61"/>
-      <c r="E76" s="61"/>
-      <c r="F76" s="61"/>
-      <c r="G76" s="61"/>
-      <c r="H76" s="61"/>
-      <c r="I76" s="61"/>
-      <c r="J76" s="61"/>
-      <c r="K76" s="61"/>
-      <c r="L76" s="62"/>
-      <c r="M76" s="53"/>
-      <c r="N76" s="53"/>
-      <c r="O76" s="53"/>
-      <c r="P76" s="53"/>
-      <c r="Q76" s="53"/>
-      <c r="R76" s="53"/>
+      <c r="C76" s="60"/>
+      <c r="D76" s="60"/>
+      <c r="E76" s="60"/>
+      <c r="F76" s="60"/>
+      <c r="G76" s="60"/>
+      <c r="H76" s="60"/>
+      <c r="I76" s="60"/>
+      <c r="J76" s="60"/>
+      <c r="K76" s="60"/>
+      <c r="L76" s="61"/>
+      <c r="M76" s="52"/>
+      <c r="N76" s="52"/>
+      <c r="O76" s="52"/>
+      <c r="P76" s="52"/>
+      <c r="Q76" s="52"/>
+      <c r="R76" s="52"/>
     </row>
     <row r="77" ht="18" customHeight="1" spans="2:18">
       <c r="B77" s="28"/>
@@ -3181,96 +3178,96 @@
       <c r="J77" s="20"/>
       <c r="K77" s="20"/>
       <c r="L77" s="21"/>
-      <c r="M77" s="53"/>
-      <c r="N77" s="53"/>
-      <c r="O77" s="53"/>
-      <c r="P77" s="53"/>
-      <c r="Q77" s="53"/>
-      <c r="R77" s="53"/>
+      <c r="M77" s="52"/>
+      <c r="N77" s="52"/>
+      <c r="O77" s="52"/>
+      <c r="P77" s="52"/>
+      <c r="Q77" s="52"/>
+      <c r="R77" s="52"/>
     </row>
     <row r="78" ht="18" customHeight="1" spans="2:18">
       <c r="B78" s="28"/>
-      <c r="C78" s="47" t="s">
+      <c r="C78" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="D78" s="63" t="s">
+      <c r="D78" s="62" t="s">
         <v>21</v>
       </c>
-      <c r="E78" s="63"/>
-      <c r="F78" s="64"/>
-      <c r="G78" s="64"/>
-      <c r="L78" s="65"/>
+      <c r="E78" s="62"/>
+      <c r="F78" s="63"/>
+      <c r="G78" s="63"/>
+      <c r="L78" s="64"/>
     </row>
     <row r="79" ht="18" customHeight="1" spans="2:18">
       <c r="B79" s="28"/>
-      <c r="C79" s="47" t="s">
+      <c r="C79" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="D79" s="63" t="s">
+      <c r="D79" s="62" t="s">
         <v>23</v>
       </c>
-      <c r="E79" s="63"/>
-      <c r="F79" s="64"/>
-      <c r="G79" s="64"/>
-      <c r="K79" s="66"/>
-      <c r="L79" s="65"/>
+      <c r="E79" s="62"/>
+      <c r="F79" s="63"/>
+      <c r="G79" s="63"/>
+      <c r="K79" s="65"/>
+      <c r="L79" s="64"/>
     </row>
     <row r="80" ht="18" customHeight="1" spans="2:18">
       <c r="B80" s="28"/>
-      <c r="C80" s="47" t="s">
+      <c r="C80" s="46" t="s">
         <v>24</v>
       </c>
-      <c r="D80" s="63" t="s">
+      <c r="D80" s="62" t="s">
         <v>25</v>
       </c>
-      <c r="E80" s="63"/>
-      <c r="F80" s="64"/>
-      <c r="G80" s="64"/>
-      <c r="L80" s="65"/>
+      <c r="E80" s="62"/>
+      <c r="F80" s="63"/>
+      <c r="G80" s="63"/>
+      <c r="L80" s="64"/>
     </row>
     <row r="81" ht="18" customHeight="1" spans="2:12">
       <c r="B81" s="28"/>
-      <c r="C81" s="47" t="s">
+      <c r="C81" s="46" t="s">
         <v>26</v>
       </c>
-      <c r="D81" s="67">
+      <c r="D81" s="66">
         <v>13654287085</v>
       </c>
       <c r="E81" s="23"/>
-      <c r="F81" s="64"/>
-      <c r="G81" s="64"/>
-      <c r="H81" s="66"/>
-      <c r="I81" s="66"/>
-      <c r="K81" s="66"/>
-      <c r="L81" s="68"/>
+      <c r="F81" s="63"/>
+      <c r="G81" s="63"/>
+      <c r="H81" s="65"/>
+      <c r="I81" s="65"/>
+      <c r="K81" s="65"/>
+      <c r="L81" s="67"/>
     </row>
     <row r="82" ht="18" customHeight="1" spans="2:12">
       <c r="B82" s="28"/>
-      <c r="C82" s="47"/>
-      <c r="D82" s="63"/>
-      <c r="E82" s="63"/>
-      <c r="F82" s="64"/>
-      <c r="G82" s="64"/>
-      <c r="H82" s="66"/>
-      <c r="I82" s="66"/>
-      <c r="K82" s="66"/>
-      <c r="L82" s="68"/>
+      <c r="C82" s="46"/>
+      <c r="D82" s="62"/>
+      <c r="E82" s="62"/>
+      <c r="F82" s="63"/>
+      <c r="G82" s="63"/>
+      <c r="H82" s="65"/>
+      <c r="I82" s="65"/>
+      <c r="K82" s="65"/>
+      <c r="L82" s="67"/>
     </row>
     <row r="83" ht="17.25" spans="2:12">
-      <c r="B83" s="69"/>
-      <c r="C83" s="70"/>
-      <c r="D83" s="70"/>
-      <c r="E83" s="70"/>
-      <c r="F83" s="71"/>
-      <c r="G83" s="71"/>
-      <c r="H83" s="70"/>
-      <c r="I83" s="70"/>
-      <c r="J83" s="70"/>
-      <c r="K83" s="70"/>
-      <c r="L83" s="72"/>
+      <c r="B83" s="68"/>
+      <c r="C83" s="69"/>
+      <c r="D83" s="69"/>
+      <c r="E83" s="69"/>
+      <c r="F83" s="70"/>
+      <c r="G83" s="70"/>
+      <c r="H83" s="69"/>
+      <c r="I83" s="69"/>
+      <c r="J83" s="69"/>
+      <c r="K83" s="69"/>
+      <c r="L83" s="71"/>
     </row>
     <row r="87" spans="2:12">
-      <c r="H87" s="73"/>
+      <c r="H87" s="72"/>
     </row>
   </sheetData>
   <mergeCells count="60">
